--- a/PythonApplication1/rezultati_kopsavilkums.xlsx
+++ b/PythonApplication1/rezultati_kopsavilkums.xlsx
@@ -8,10 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="Kopsavilkums" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="train_stratified_10pct_grupa1_1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="train_stratified_25pct_grupa1_1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="train_stratified_50pct_grupa1_1" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="train_stratified_75pct_grupa1_1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="train_stratified_10pct" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="train_stratified_10pct_2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="train_benign_reduced_80pct_beni" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="train" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -631,26 +631,26 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>merged_no_nan_clean_headers_no_duplicates_train_stratified_10pct_grupa1_10pct</t>
+          <t>merged_no_nan_clean_headers_no_duplicates_train_stratified_10pct</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.9767</v>
+        <v>0.9866</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.6757</v>
+        <v>0.8188</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.6464</v>
+        <v>0.7771</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9736</v>
+        <v>0.9848</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9822</v>
+        <v>0.9922</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>13.1162</v>
+        <v>11.8821</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1082359</v>
@@ -659,26 +659,26 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>merged_no_nan_clean_headers_no_duplicates_train_stratified_25pct_grupa1_10pct</t>
+          <t>merged_no_nan_clean_headers_no_duplicates_train_stratified_10pct</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.9866</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.7225</v>
+        <v>0.8188</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.6921</v>
+        <v>0.7771</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9734</v>
+        <v>0.9848</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9852</v>
+        <v>0.9922</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>12.7837</v>
+        <v>12.039</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>1082359</v>
@@ -687,26 +687,26 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>merged_no_nan_clean_headers_no_duplicates_train_stratified_50pct_grupa1_10pct</t>
+          <t>merged_no_nan_clean_headers_no_duplicates_train_benign_reduced_80pct_benign_reduced_10pct</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.9766</v>
+        <v>0.9683</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.7351</v>
+        <v>0.6642</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.7033</v>
+        <v>0.6896</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9737</v>
+        <v>0.9754</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9839</v>
+        <v>0.9893</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>13.2112</v>
+        <v>14.4379</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1082359</v>
@@ -715,26 +715,26 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>merged_no_nan_clean_headers_no_duplicates_train_stratified_75pct_grupa1_10pct</t>
+          <t>merged_no_nan_clean_headers_no_duplicates_train</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.9765</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.7281</v>
+        <v>0.8218</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.6989</v>
+        <v>0.7679</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.9735</v>
+        <v>0.9849</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.9816</v>
+        <v>0.9925</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>13.0126</v>
+        <v>13.913</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1082359</v>
@@ -751,7 +751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -769,7 +769,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>merged_no_nan_clean_headers_no_duplicates_train_stratified_10pct_grupa1_10pct</t>
+          <t>merged_no_nan_clean_headers_no_duplicates_train_stratified_10pct</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>13.1162</t>
+          <t>11.8821</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>0.9767</t>
+          <t>0.9866</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>0.6757</t>
+          <t>0.8188</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>0.6464</t>
+          <t>0.7771</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>0.9736</t>
+          <t>0.9848</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>0.9822</t>
+          <t>0.9922</t>
         </is>
       </c>
     </row>
@@ -890,17 +890,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>0.9875</t>
+          <t>0.9899</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0.9911</t>
+          <t>0.9949</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0.9893</t>
+          <t>0.9924</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -915,17 +915,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>0.9887</t>
+          <t>0.9933</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0.9911</t>
+          <t>0.9980</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0.9899</t>
+          <t>0.9956</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -940,17 +940,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>0.3043</t>
+          <t>0.7872</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0.5000</t>
+          <t>0.6607</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0.3784</t>
+          <t>0.7184</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
@@ -965,17 +965,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>0.4250</t>
+          <t>0.7241</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0.7391</t>
+          <t>0.9130</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0.5397</t>
+          <t>0.8077</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
@@ -990,17 +990,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>0.8428</t>
+          <t>0.9998</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0.8825</t>
+          <t>0.9999</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0.8622</t>
+          <t>0.9999</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>0.7754</t>
+          <t>0.8101</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0.8056</t>
+          <t>0.8239</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
@@ -1040,17 +1040,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>0.9528</t>
+          <t>0.9993</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0.9770</t>
+          <t>0.9993</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0.9647</t>
+          <t>0.9993</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>0.8682</t>
+          <t>0.9995</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0.8735</t>
+          <t>0.9998</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0.8708</t>
+          <t>0.9996</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
@@ -1090,17 +1090,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>0.7490</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0.8769</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0.8079</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
@@ -1115,17 +1115,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.7500</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.5000</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.6000</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
@@ -1140,17 +1140,17 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>0.9646</t>
+          <t>0.9499</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0.9889</t>
+          <t>0.9939</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0.9766</t>
+          <t>0.9714</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
@@ -1190,17 +1190,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>0.2802</t>
+          <t>0.2796</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0.0706</t>
+          <t>0.1586</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0.1128</t>
+          <t>0.2024</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0.2500</t>
+          <t>0.3750</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0.4000</t>
+          <t>0.5455</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
@@ -1240,17 +1240,17 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>0.9972</t>
+          <t>0.9998</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0.9979</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0.9976</t>
+          <t>0.9999</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
@@ -1272,71 +1272,101 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>TotLen Fwd Pkts</t>
+          <t>Fwd Act Data Pkts</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0.3108</v>
+        <v>0.204</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Tot Bwd Pkts</t>
+          <t>Fwd Pkt Len Max</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>0.2389</v>
+        <v>0.0779</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>TotLen Bwd Pkts</t>
+          <t>Fwd Seg Size Min</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0.1318</v>
+        <v>0.07439999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Tot Fwd Pkts</t>
+          <t>Subflow Fwd Byts</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.1224</v>
+        <v>0.06510000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Flow Duration</t>
+          <t>Bwd IAT Max</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.0844</v>
+        <v>0.0317</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Protocol</t>
+          <t>Bwd IAT Min</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0.0813</v>
+        <v>0.0261</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>SYN Flag Cnt</t>
+          <t>Flow Duration</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0.0304</v>
+        <v>0.0255</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Bwd Pkt Len Std</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Bwd Pkt Len Max</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>0.0236</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>TotLen Fwd Pkts</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>0.0235</v>
       </c>
     </row>
   </sheetData>
@@ -1351,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1369,7 +1399,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>merged_no_nan_clean_headers_no_duplicates_train_stratified_25pct_grupa1_10pct</t>
+          <t>merged_no_nan_clean_headers_no_duplicates_train_stratified_10pct</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1421,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>12.7837</t>
+          <t>12.0390</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1433,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>0.9763</t>
+          <t>0.9866</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1445,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>0.7225</t>
+          <t>0.8188</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1457,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>0.6921</t>
+          <t>0.7771</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1469,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>0.9734</t>
+          <t>0.9848</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1481,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>0.9852</t>
+          <t>0.9922</t>
         </is>
       </c>
     </row>
@@ -1490,17 +1520,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>0.9874</t>
+          <t>0.9899</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0.9910</t>
+          <t>0.9949</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0.9892</t>
+          <t>0.9924</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -1515,17 +1545,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>0.9990</t>
+          <t>0.9933</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0.9907</t>
+          <t>0.9980</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0.9948</t>
+          <t>0.9956</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -1540,17 +1570,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>0.7872</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0.5000</t>
+          <t>0.6607</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0.6667</t>
+          <t>0.7184</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
@@ -1565,17 +1595,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>0.4722</t>
+          <t>0.7241</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0.7391</t>
+          <t>0.9130</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0.5763</t>
+          <t>0.8077</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
@@ -1590,17 +1620,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>0.9370</t>
+          <t>0.9998</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0.8335</t>
+          <t>0.9999</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0.8822</t>
+          <t>0.9999</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
@@ -1615,17 +1645,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>0.7020</t>
+          <t>0.8101</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0.9942</t>
+          <t>0.8382</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0.8230</t>
+          <t>0.8239</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
@@ -1640,17 +1670,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>0.9505</t>
+          <t>0.9993</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0.9754</t>
+          <t>0.9993</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0.9628</t>
+          <t>0.9993</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
@@ -1665,17 +1695,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>0.8779</t>
+          <t>0.9995</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0.8199</t>
+          <t>0.9998</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0.8479</t>
+          <t>0.9996</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
@@ -1690,17 +1720,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>0.6643</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0.9359</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0.7771</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
@@ -1715,17 +1745,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.7500</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.5000</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.6000</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
@@ -1740,17 +1770,17 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>0.9607</t>
+          <t>0.9499</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0.9879</t>
+          <t>0.9939</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0.9741</t>
+          <t>0.9714</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
@@ -1790,17 +1820,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>0.2862</t>
+          <t>0.2796</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0.0752</t>
+          <t>0.1586</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0.1191</t>
+          <t>0.2024</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
@@ -1820,12 +1850,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0.6250</t>
+          <t>0.3750</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0.7692</t>
+          <t>0.5455</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
@@ -1840,17 +1870,17 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
+          <t>0.9998</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>0.9999</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>0.9974</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>0.9987</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
@@ -1872,71 +1902,101 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Tot Bwd Pkts</t>
+          <t>Fwd Act Data Pkts</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0.3145</v>
+        <v>0.204</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>TotLen Bwd Pkts</t>
+          <t>Fwd Pkt Len Max</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>0.1797</v>
+        <v>0.0779</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Protocol</t>
+          <t>Fwd Seg Size Min</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0.1487</v>
+        <v>0.07439999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>TotLen Fwd Pkts</t>
+          <t>Subflow Fwd Byts</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.1373</v>
+        <v>0.06510000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Tot Fwd Pkts</t>
+          <t>Bwd IAT Max</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.1132</v>
+        <v>0.0317</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Flow Duration</t>
+          <t>Bwd IAT Min</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0.0848</v>
+        <v>0.0261</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>SYN Flag Cnt</t>
+          <t>Flow Duration</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0.0218</v>
+        <v>0.0255</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Bwd Pkt Len Std</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Bwd Pkt Len Max</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>0.0236</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>TotLen Fwd Pkts</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>0.0235</v>
       </c>
     </row>
   </sheetData>
@@ -1951,7 +2011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1969,7 +2029,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>merged_no_nan_clean_headers_no_duplicates_train_stratified_50pct_grupa1_10pct</t>
+          <t>merged_no_nan_clean_headers_no_duplicates_train_benign_reduced_80pct_benign_reduced_10pct</t>
         </is>
       </c>
     </row>
@@ -1991,7 +2051,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>13.2112</t>
+          <t>14.4379</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2063,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>0.9766</t>
+          <t>0.9683</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2075,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>0.7351</t>
+          <t>0.6642</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2087,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>0.7033</t>
+          <t>0.6896</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2099,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>0.9737</t>
+          <t>0.9754</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2111,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>0.9839</t>
+          <t>0.9893</t>
         </is>
       </c>
     </row>
@@ -2090,17 +2150,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>0.9873</t>
+          <t>0.9926</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0.9915</t>
+          <t>0.9713</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0.9894</t>
+          <t>0.9818</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -2115,17 +2175,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>0.9987</t>
+          <t>0.9899</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0.9912</t>
+          <t>0.9996</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0.9950</t>
+          <t>0.9947</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -2140,17 +2200,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>0.9333</t>
+          <t>0.1468</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0.5000</t>
+          <t>0.9464</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0.6512</t>
+          <t>0.2542</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
@@ -2165,17 +2225,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>0.7037</t>
+          <t>0.4762</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0.8261</t>
+          <t>0.8696</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0.7600</t>
+          <t>0.6154</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
@@ -2190,17 +2250,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>0.9754</t>
+          <t>0.9997</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0.8183</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0.8900</t>
+          <t>0.9999</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
@@ -2215,17 +2275,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>0.6964</t>
+          <t>0.7826</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0.9942</t>
+          <t>0.9364</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0.8190</t>
+          <t>0.8526</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
@@ -2240,17 +2300,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>0.9517</t>
+          <t>0.9993</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0.9750</t>
+          <t>0.9995</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0.9632</t>
+          <t>0.9994</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
@@ -2265,17 +2325,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>0.8714</t>
+          <t>0.9995</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0.8230</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0.8465</t>
+          <t>0.9998</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
@@ -2290,17 +2350,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>0.6561</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0.9528</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0.7771</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
@@ -2340,17 +2400,17 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>0.9579</t>
+          <t>0.7648</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0.9879</t>
+          <t>0.9939</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0.9727</t>
+          <t>0.8644</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
@@ -2390,17 +2450,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>0.2954</t>
+          <t>0.1444</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0.0733</t>
+          <t>0.3923</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.2111</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
@@ -2415,17 +2475,17 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>0.6667</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0.6250</t>
+          <t>0.5000</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0.7692</t>
+          <t>0.5714</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
@@ -2440,17 +2500,17 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>0.9986</t>
+          <t>0.9999</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0.9978</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0.9982</t>
+          <t>0.9999</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
@@ -2472,71 +2532,101 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>TotLen Bwd Pkts</t>
+          <t>Tot Fwd Pkts</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0.2011</v>
+        <v>0.2828</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Tot Fwd Pkts</t>
+          <t>Active Max</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>0.2002</v>
+        <v>0.1087</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>TotLen Fwd Pkts</t>
+          <t>Fwd Act Data Pkts</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0.1861</v>
+        <v>0.0561</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Tot Bwd Pkts</t>
+          <t>Bwd IAT Max</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.1734</v>
+        <v>0.0522</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Protocol</t>
+          <t>Fwd Pkt Len Mean</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.1141</v>
+        <v>0.0486</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Flow Duration</t>
+          <t>Flow IAT Std</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0.1043</v>
+        <v>0.0389</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>SYN Flag Cnt</t>
+          <t>Fwd Seg Size Min</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0.0208</v>
+        <v>0.0343</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Fwd Seg Size Avg</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>0.0342</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Pkt Len Min</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>0.0318</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Pkt Size Avg</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>0.0297</v>
       </c>
     </row>
   </sheetData>
@@ -2551,7 +2641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2569,7 +2659,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>merged_no_nan_clean_headers_no_duplicates_train_stratified_75pct_grupa1_10pct</t>
+          <t>merged_no_nan_clean_headers_no_duplicates_train</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2681,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>13.0126</t>
+          <t>13.9130</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2693,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>0.9765</t>
+          <t>0.9894</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2705,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>0.7281</t>
+          <t>0.8218</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2717,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>0.6989</t>
+          <t>0.7679</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2729,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>0.9735</t>
+          <t>0.9849</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2741,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>0.9816</t>
+          <t>0.9925</t>
         </is>
       </c>
     </row>
@@ -2690,17 +2780,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>0.9872</t>
+          <t>0.9885</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0.9913</t>
+          <t>0.9996</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0.9893</t>
+          <t>0.9940</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -2715,17 +2805,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>0.9989</t>
+          <t>0.9998</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0.9909</t>
+          <t>0.9970</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0.9949</t>
+          <t>0.9984</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -2740,17 +2830,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>0.8235</t>
+          <t>0.9231</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0.5000</t>
+          <t>0.6429</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0.6222</t>
+          <t>0.7579</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
@@ -2765,17 +2855,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>0.7391</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0.7391</t>
+          <t>0.9130</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0.7391</t>
+          <t>0.9545</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
@@ -2790,17 +2880,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>0.9760</t>
+          <t>0.9998</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0.8183</t>
+          <t>0.9998</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0.8902</t>
+          <t>0.9998</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
@@ -2815,17 +2905,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>0.6811</t>
+          <t>0.8950</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>0.9364</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0.8103</t>
+          <t>0.9153</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
@@ -2840,17 +2930,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>0.9504</t>
+          <t>0.9997</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0.9748</t>
+          <t>0.9995</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0.9625</t>
+          <t>0.9996</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
@@ -2865,17 +2955,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>0.8660</t>
+          <t>0.9998</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0.8254</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0.8452</t>
+          <t>0.9999</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
@@ -2890,17 +2980,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>0.6542</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0.9534</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0.7760</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
@@ -2940,17 +3030,17 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>0.9617</t>
+          <t>0.9479</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0.9889</t>
+          <t>0.9909</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0.9751</t>
+          <t>0.9689</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
@@ -2990,17 +3080,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>0.2844</t>
+          <t>0.5738</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0.0695</t>
+          <t>0.0393</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0.1117</t>
+          <t>0.0735</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
@@ -3020,12 +3110,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0.6250</t>
+          <t>0.7500</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0.7692</t>
+          <t>0.8571</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
@@ -3040,17 +3130,17 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>0.9988</t>
+          <t>0.9999</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0.9978</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0.9983</t>
+          <t>0.9999</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
@@ -3072,71 +3162,101 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Tot Bwd Pkts</t>
+          <t>Subflow Fwd Byts</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0.3168</v>
+        <v>0.2082</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Protocol</t>
+          <t>TotLen Fwd Pkts</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>0.218</v>
+        <v>0.1695</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>TotLen Bwd Pkts</t>
+          <t>Flow Pkts/s</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0.1737</v>
+        <v>0.0949</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Tot Fwd Pkts</t>
+          <t>Flow IAT Std</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.1442</v>
+        <v>0.0577</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Flow Duration</t>
+          <t>Tot Fwd Pkts</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.0755</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>TotLen Fwd Pkts</t>
+          <t>Bwd Pkt Len Std</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0.0499</v>
+        <v>0.0352</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>SYN Flag Cnt</t>
+          <t>Bwd IAT Std</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0.0218</v>
+        <v>0.0345</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Fwd Act Data Pkts</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>0.0335</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Flow Byts/s</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>0.0311</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Fwd Pkt Len Max</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>0.0305</v>
       </c>
     </row>
   </sheetData>
